--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/127.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/127.xlsx
@@ -426,13 +426,13 @@
         <v>-18.25099268756874</v>
       </c>
       <c r="E2">
-        <v>-21.58306694671113</v>
+        <v>-31.9104987230368</v>
       </c>
       <c r="F2">
-        <v>-3.015645997749621</v>
+        <v>-5.881566925297932</v>
       </c>
       <c r="G2">
-        <v>-16.71548486842664</v>
+        <v>-22.00403801335271</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.00862402825151</v>
       </c>
       <c r="E3">
-        <v>-22.3034384779553</v>
+        <v>-31.91069118318213</v>
       </c>
       <c r="F3">
-        <v>-3.014414215421658</v>
+        <v>-5.702883934677065</v>
       </c>
       <c r="G3">
-        <v>-16.3964779459743</v>
+        <v>-21.21968004628603</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.7465895145419</v>
       </c>
       <c r="E4">
-        <v>-22.83339673412495</v>
+        <v>-31.74174740337797</v>
       </c>
       <c r="F4">
-        <v>-2.831887600051801</v>
+        <v>-5.867241967801321</v>
       </c>
       <c r="G4">
-        <v>-16.41470513173702</v>
+        <v>-21.70928095883545</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.4849272371571</v>
       </c>
       <c r="E5">
-        <v>-23.08362209389278</v>
+        <v>-32.15058935797547</v>
       </c>
       <c r="F5">
-        <v>-2.884728328308979</v>
+        <v>-6.245459613306324</v>
       </c>
       <c r="G5">
-        <v>-15.93062815568292</v>
+        <v>-21.04725021272643</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.22604672408946</v>
       </c>
       <c r="E6">
-        <v>-24.54114315257954</v>
+        <v>-33.62943273652734</v>
       </c>
       <c r="F6">
-        <v>-2.763903487304046</v>
+        <v>-5.847420792587134</v>
       </c>
       <c r="G6">
-        <v>-15.4291984394117</v>
+        <v>-21.00079631849859</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.96960477889821</v>
       </c>
       <c r="E7">
-        <v>-24.19806143328443</v>
+        <v>-35.18220571749143</v>
       </c>
       <c r="F7">
-        <v>-2.762593010072817</v>
+        <v>-5.775766183877574</v>
       </c>
       <c r="G7">
-        <v>-15.452135818723</v>
+        <v>-20.66714366361568</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.70870068610832</v>
       </c>
       <c r="E8">
-        <v>-24.69698605707951</v>
+        <v>-34.6188386443302</v>
       </c>
       <c r="F8">
-        <v>-2.714703433782172</v>
+        <v>-5.796216089950486</v>
       </c>
       <c r="G8">
-        <v>-15.24543034475344</v>
+        <v>-21.22645905002784</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.45828747674339</v>
       </c>
       <c r="E9">
-        <v>-25.38920406541799</v>
+        <v>-34.26999217762332</v>
       </c>
       <c r="F9">
-        <v>-2.810855351694722</v>
+        <v>-5.672592195491493</v>
       </c>
       <c r="G9">
-        <v>-14.55851645494836</v>
+        <v>-20.73983584604361</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.21978677970827</v>
       </c>
       <c r="E10">
-        <v>-25.96356400923284</v>
+        <v>-35.08832139436441</v>
       </c>
       <c r="F10">
-        <v>-2.581945131972509</v>
+        <v>-5.670056562871523</v>
       </c>
       <c r="G10">
-        <v>-14.32544308452711</v>
+        <v>-20.14762293227646</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.99067258140478</v>
       </c>
       <c r="E11">
-        <v>-26.78920444725932</v>
+        <v>-35.68227151673645</v>
       </c>
       <c r="F11">
-        <v>-2.477739826169942</v>
+        <v>-5.565078390282145</v>
       </c>
       <c r="G11">
-        <v>-14.22816470895425</v>
+        <v>-20.2721272437388</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.76014666806132</v>
       </c>
       <c r="E12">
-        <v>-27.0190879017847</v>
+        <v>-36.64805916835231</v>
       </c>
       <c r="F12">
-        <v>-2.567825609591792</v>
+        <v>-5.74354186354127</v>
       </c>
       <c r="G12">
-        <v>-13.67191398347861</v>
+        <v>-20.53991429764821</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.5197826946587</v>
       </c>
       <c r="E13">
-        <v>-27.75184480943985</v>
+        <v>-36.64383410210316</v>
       </c>
       <c r="F13">
-        <v>-2.432009803698396</v>
+        <v>-5.618315906525264</v>
       </c>
       <c r="G13">
-        <v>-12.94076594583066</v>
+        <v>-19.68327758207008</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.2825319178167</v>
       </c>
       <c r="E14">
-        <v>-28.60189372236766</v>
+        <v>-36.9527530134844</v>
       </c>
       <c r="F14">
-        <v>-2.316169249356107</v>
+        <v>-5.578634622828958</v>
       </c>
       <c r="G14">
-        <v>-12.96439074105866</v>
+        <v>-18.25264529482282</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.04846106583359</v>
       </c>
       <c r="E15">
-        <v>-29.12917565039878</v>
+        <v>-37.89755118807471</v>
       </c>
       <c r="F15">
-        <v>-2.220747123125424</v>
+        <v>-5.043758619208721</v>
       </c>
       <c r="G15">
-        <v>-12.42546650602766</v>
+        <v>-19.26288583526324</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.81729860895993</v>
       </c>
       <c r="E16">
-        <v>-29.94127821537932</v>
+        <v>-38.82112440499106</v>
       </c>
       <c r="F16">
-        <v>-2.306163399497692</v>
+        <v>-5.215167715665606</v>
       </c>
       <c r="G16">
-        <v>-12.07726327413939</v>
+        <v>-18.38614507519039</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.57942982122566</v>
       </c>
       <c r="E17">
-        <v>-30.23251117152362</v>
+        <v>-38.80465434502516</v>
       </c>
       <c r="F17">
-        <v>-1.981812001094532</v>
+        <v>-5.101576178821918</v>
       </c>
       <c r="G17">
-        <v>-11.73416890421917</v>
+        <v>-18.60790151245312</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.3375295919389</v>
       </c>
       <c r="E18">
-        <v>-31.59859328304749</v>
+        <v>-39.60428549258858</v>
       </c>
       <c r="F18">
-        <v>-1.798267322186634</v>
+        <v>-5.066363937263716</v>
       </c>
       <c r="G18">
-        <v>-11.37744105871946</v>
+        <v>-18.36679078982201</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.10178994150762</v>
       </c>
       <c r="E19">
-        <v>-32.23031993559152</v>
+        <v>-39.27120943661342</v>
       </c>
       <c r="F19">
-        <v>-1.713275998292002</v>
+        <v>-5.07367676469563</v>
       </c>
       <c r="G19">
-        <v>-11.03355919562498</v>
+        <v>-17.78579473195581</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.87203978714528</v>
       </c>
       <c r="E20">
-        <v>-32.50322162895276</v>
+        <v>-40.51932027176348</v>
       </c>
       <c r="F20">
-        <v>-1.759862552658043</v>
+        <v>-4.782598399760718</v>
       </c>
       <c r="G20">
-        <v>-10.43464438682265</v>
+        <v>-17.42445677016508</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.64506583430418</v>
       </c>
       <c r="E21">
-        <v>-32.93795739792611</v>
+        <v>-40.53426197175178</v>
       </c>
       <c r="F21">
-        <v>-1.65142097595756</v>
+        <v>-4.577387771432599</v>
       </c>
       <c r="G21">
-        <v>-10.43667874418951</v>
+        <v>-16.9257258586265</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.40834639594168</v>
       </c>
       <c r="E22">
-        <v>-33.31907829888566</v>
+        <v>-41.09378663471751</v>
       </c>
       <c r="F22">
-        <v>-1.585534289473693</v>
+        <v>-4.911838625210691</v>
       </c>
       <c r="G22">
-        <v>-10.34590703096903</v>
+        <v>-16.75822770107074</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.16570838044326</v>
       </c>
       <c r="E23">
-        <v>-34.08728862954686</v>
+        <v>-42.27033625936136</v>
       </c>
       <c r="F23">
-        <v>-1.413966974842873</v>
+        <v>-4.322910820190383</v>
       </c>
       <c r="G23">
-        <v>-10.20758713613064</v>
+        <v>-17.1704541280269</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.92421240106411</v>
       </c>
       <c r="E24">
-        <v>-35.08842781350359</v>
+        <v>-41.5508591017337</v>
       </c>
       <c r="F24">
-        <v>-1.388833479474534</v>
+        <v>-4.644753093730463</v>
       </c>
       <c r="G24">
-        <v>-9.752901702195263</v>
+        <v>-16.89026897845514</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.68670110216854</v>
       </c>
       <c r="E25">
-        <v>-34.68466001403169</v>
+        <v>-42.16943053728544</v>
       </c>
       <c r="F25">
-        <v>-1.13137771905185</v>
+        <v>-4.411232181044269</v>
       </c>
       <c r="G25">
-        <v>-9.951671541823305</v>
+        <v>-16.73594328484977</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.45563968490211</v>
       </c>
       <c r="E26">
-        <v>-34.75249202619258</v>
+        <v>-43.04173463572396</v>
       </c>
       <c r="F26">
-        <v>-1.376306079241997</v>
+        <v>-4.484755586614544</v>
       </c>
       <c r="G26">
-        <v>-9.808419970981067</v>
+        <v>-16.45958896144866</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.22970161472866</v>
       </c>
       <c r="E27">
-        <v>-34.50043489868865</v>
+        <v>-41.26848610498541</v>
       </c>
       <c r="F27">
-        <v>-1.055268978817437</v>
+        <v>-4.440234980551085</v>
       </c>
       <c r="G27">
-        <v>-9.700667936190463</v>
+        <v>-16.72061998016717</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.02487584246259</v>
       </c>
       <c r="E28">
-        <v>-35.14304347427311</v>
+        <v>-42.36504250052077</v>
       </c>
       <c r="F28">
-        <v>-1.062616597680269</v>
+        <v>-4.340743913637851</v>
       </c>
       <c r="G28">
-        <v>-9.861401855501422</v>
+        <v>-17.04278835959203</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.85214487896861</v>
       </c>
       <c r="E29">
-        <v>-34.84126143792794</v>
+        <v>-42.38709616893813</v>
       </c>
       <c r="F29">
-        <v>-1.468986309369414</v>
+        <v>-4.548464495196452</v>
       </c>
       <c r="G29">
-        <v>-9.75670463798266</v>
+        <v>-17.55826006352689</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.71558144436233</v>
       </c>
       <c r="E30">
-        <v>-35.04629262709923</v>
+        <v>-41.89185545874828</v>
       </c>
       <c r="F30">
-        <v>-1.361540430287095</v>
+        <v>-4.369538792926564</v>
       </c>
       <c r="G30">
-        <v>-10.0936401550358</v>
+        <v>-17.31029158783654</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.61286705736406</v>
       </c>
       <c r="E31">
-        <v>-34.97704773104794</v>
+        <v>-42.09791687575631</v>
       </c>
       <c r="F31">
-        <v>-1.311014988920743</v>
+        <v>-4.192207697907065</v>
       </c>
       <c r="G31">
-        <v>-9.936262925380152</v>
+        <v>-17.55824857925144</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.53738736929724</v>
       </c>
       <c r="E32">
-        <v>-34.08934682098334</v>
+        <v>-41.79585407402268</v>
       </c>
       <c r="F32">
-        <v>-1.166399436107408</v>
+        <v>-4.372503519861183</v>
       </c>
       <c r="G32">
-        <v>-9.992873840945252</v>
+        <v>-16.6886756476752</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.49693787371804</v>
       </c>
       <c r="E33">
-        <v>-34.21920987010131</v>
+        <v>-42.33422397066157</v>
       </c>
       <c r="F33">
-        <v>-1.303480987392281</v>
+        <v>-4.352038703175022</v>
       </c>
       <c r="G33">
-        <v>-9.969859352927307</v>
+        <v>-17.20664107999524</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.4897063486211</v>
       </c>
       <c r="E34">
-        <v>-33.92842070440977</v>
+        <v>-41.02366095047173</v>
       </c>
       <c r="F34">
-        <v>-1.415917780076466</v>
+        <v>-4.715925592611594</v>
       </c>
       <c r="G34">
-        <v>-10.1135112327998</v>
+        <v>-17.76331836427361</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.5089682708255</v>
       </c>
       <c r="E35">
-        <v>-33.07614378227018</v>
+        <v>-40.9330190147342</v>
       </c>
       <c r="F35">
-        <v>-1.343370191306688</v>
+        <v>-4.809969315484019</v>
       </c>
       <c r="G35">
-        <v>-10.52057957946451</v>
+        <v>-17.62501323493224</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.54072755000148</v>
       </c>
       <c r="E36">
-        <v>-32.95099034612019</v>
+        <v>-40.03770347562571</v>
       </c>
       <c r="F36">
-        <v>-1.235396642188787</v>
+        <v>-4.54817705170768</v>
       </c>
       <c r="G36">
-        <v>-10.41033709751028</v>
+        <v>-17.60546207627029</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.57212827212849</v>
       </c>
       <c r="E37">
-        <v>-32.58217104480249</v>
+        <v>-40.62174529686897</v>
       </c>
       <c r="F37">
-        <v>-1.243476537835693</v>
+        <v>-4.391579164412851</v>
       </c>
       <c r="G37">
-        <v>-10.45279282326794</v>
+        <v>-17.70773118983506</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.60561847819848</v>
       </c>
       <c r="E38">
-        <v>-32.21235774344009</v>
+        <v>-40.54196490603883</v>
       </c>
       <c r="F38">
-        <v>-1.084753888152683</v>
+        <v>-4.59792631281761</v>
       </c>
       <c r="G38">
-        <v>-10.49260388444868</v>
+        <v>-17.60984906949527</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.63612590041938</v>
       </c>
       <c r="E39">
-        <v>-31.48761397054151</v>
+        <v>-38.91681332501014</v>
       </c>
       <c r="F39">
-        <v>-1.341295959330078</v>
+        <v>-4.760336025810481</v>
       </c>
       <c r="G39">
-        <v>-10.8089661423241</v>
+        <v>-17.8638385867472</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.6600878634467</v>
       </c>
       <c r="E40">
-        <v>-31.23665952645845</v>
+        <v>-39.1029947411245</v>
       </c>
       <c r="F40">
-        <v>-1.189456214396929</v>
+        <v>-4.507732013265994</v>
       </c>
       <c r="G40">
-        <v>-10.89107543062765</v>
+        <v>-17.94303250969518</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.66855473611987</v>
       </c>
       <c r="E41">
-        <v>-30.96726287197914</v>
+        <v>-38.53343724399478</v>
       </c>
       <c r="F41">
-        <v>-0.9937353630352814</v>
+        <v>-4.166373403715957</v>
       </c>
       <c r="G41">
-        <v>-10.80697772205908</v>
+        <v>-18.25630877869394</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.66512718777722</v>
       </c>
       <c r="E42">
-        <v>-29.97667729669728</v>
+        <v>-39.01639673267582</v>
       </c>
       <c r="F42">
-        <v>-1.205224187909218</v>
+        <v>-4.479726568112149</v>
       </c>
       <c r="G42">
-        <v>-11.00118994494105</v>
+        <v>-18.23094821726099</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.66262669397002</v>
       </c>
       <c r="E43">
-        <v>-29.68270234954134</v>
+        <v>-38.73809483406043</v>
       </c>
       <c r="F43">
-        <v>-1.320292703832097</v>
+        <v>-4.333138672512748</v>
       </c>
       <c r="G43">
-        <v>-11.48221702555565</v>
+        <v>-18.38801865270083</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.66745662005248</v>
       </c>
       <c r="E44">
-        <v>-29.21566950394528</v>
+        <v>-37.84820440681312</v>
       </c>
       <c r="F44">
-        <v>-1.023160629917526</v>
+        <v>-4.380223904055275</v>
       </c>
       <c r="G44">
-        <v>-11.46923979428805</v>
+        <v>-18.40465936783956</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.6847761260871</v>
       </c>
       <c r="E45">
-        <v>-28.67814416770882</v>
+        <v>-36.97635542001238</v>
       </c>
       <c r="F45">
-        <v>-0.96805100334408</v>
+        <v>-4.444253390822065</v>
       </c>
       <c r="G45">
-        <v>-11.37675528341354</v>
+        <v>-17.98884328449737</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.70995037296207</v>
       </c>
       <c r="E46">
-        <v>-27.92554348695206</v>
+        <v>-36.94325680349031</v>
       </c>
       <c r="F46">
-        <v>-1.040733616000514</v>
+        <v>-4.252907147714602</v>
       </c>
       <c r="G46">
-        <v>-11.02097899216606</v>
+        <v>-18.30907738381293</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.75281254772481</v>
       </c>
       <c r="E47">
-        <v>-27.76850959378807</v>
+        <v>-37.43696009675455</v>
       </c>
       <c r="F47">
-        <v>-1.063012557298807</v>
+        <v>-4.472772423765647</v>
       </c>
       <c r="G47">
-        <v>-11.79869412618565</v>
+        <v>-18.18395128086507</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.8219658756815</v>
       </c>
       <c r="E48">
-        <v>-27.24332887769652</v>
+        <v>-36.53005166418643</v>
       </c>
       <c r="F48">
-        <v>-0.9173292389032635</v>
+        <v>-4.226236202446667</v>
       </c>
       <c r="G48">
-        <v>-11.60246723326618</v>
+        <v>-18.71624744834599</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.91871364818649</v>
       </c>
       <c r="E49">
-        <v>-26.74390612176059</v>
+        <v>-36.29567143497143</v>
       </c>
       <c r="F49">
-        <v>-0.8122723714106189</v>
+        <v>-4.223806600854255</v>
       </c>
       <c r="G49">
-        <v>-11.78595642409189</v>
+        <v>-18.38823685393454</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.03941312004172</v>
       </c>
       <c r="E50">
-        <v>-26.43203917380035</v>
+        <v>-35.65936196673164</v>
       </c>
       <c r="F50">
-        <v>-0.7590174594520416</v>
+        <v>-4.034011061524833</v>
       </c>
       <c r="G50">
-        <v>-11.6798942184044</v>
+        <v>-18.84649225692658</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.1724365816514</v>
       </c>
       <c r="E51">
-        <v>-25.91443006624962</v>
+        <v>-34.57500528017296</v>
       </c>
       <c r="F51">
-        <v>-0.8542747405695679</v>
+        <v>-4.178856072108743</v>
       </c>
       <c r="G51">
-        <v>-12.43618953808393</v>
+        <v>-18.62404840374715</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.32135974131698</v>
       </c>
       <c r="E52">
-        <v>-25.34728851000299</v>
+        <v>-35.31037058885652</v>
       </c>
       <c r="F52">
-        <v>-0.8461923598204532</v>
+        <v>-3.923584716527242</v>
       </c>
       <c r="G52">
-        <v>-12.47274234625614</v>
+        <v>-18.93846489723782</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.48585687627276</v>
       </c>
       <c r="E53">
-        <v>-24.88663854852074</v>
+        <v>-34.96509255966769</v>
       </c>
       <c r="F53">
-        <v>-0.9370311292114469</v>
+        <v>-4.174495546100406</v>
       </c>
       <c r="G53">
-        <v>-12.38791948772294</v>
+        <v>-18.83094254795638</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.6609609931989</v>
       </c>
       <c r="E54">
-        <v>-24.74849744891676</v>
+        <v>-33.67688208717971</v>
       </c>
       <c r="F54">
-        <v>-0.8144816272738853</v>
+        <v>-4.375419373119038</v>
       </c>
       <c r="G54">
-        <v>-12.27568858550369</v>
+        <v>-19.53383926797751</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.83692418618789</v>
       </c>
       <c r="E55">
-        <v>-24.05482580042181</v>
+        <v>-34.65715859138311</v>
       </c>
       <c r="F55">
-        <v>-1.098467510506029</v>
+        <v>-4.329046537542919</v>
       </c>
       <c r="G55">
-        <v>-12.77403723473059</v>
+        <v>-19.15040063837314</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.00154421968199</v>
       </c>
       <c r="E56">
-        <v>-23.9134785412204</v>
+        <v>-33.82608172031043</v>
       </c>
       <c r="F56">
-        <v>-0.9583897543252293</v>
+        <v>-4.498799727561607</v>
       </c>
       <c r="G56">
-        <v>-12.98042607081967</v>
+        <v>-18.47556984696072</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.15895564150577</v>
       </c>
       <c r="E57">
-        <v>-23.37964843977419</v>
+        <v>-33.20178855784999</v>
       </c>
       <c r="F57">
-        <v>-0.952243268196457</v>
+        <v>-4.225733383433167</v>
       </c>
       <c r="G57">
-        <v>-12.9239824975541</v>
+        <v>-18.78586512617273</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.30756390639466</v>
       </c>
       <c r="E58">
-        <v>-23.19034916930556</v>
+        <v>-32.81901702811465</v>
       </c>
       <c r="F58">
-        <v>-0.8578060708077022</v>
+        <v>-4.115630930090071</v>
       </c>
       <c r="G58">
-        <v>-12.80284636002252</v>
+        <v>-19.66698467641665</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.44338465336294</v>
       </c>
       <c r="E59">
-        <v>-22.73417786861689</v>
+        <v>-32.66287524433018</v>
       </c>
       <c r="F59">
-        <v>-0.9301995832405594</v>
+        <v>-4.084061848369381</v>
       </c>
       <c r="G59">
-        <v>-13.03845119287689</v>
+        <v>-19.45185138487166</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.55643840257834</v>
       </c>
       <c r="E60">
-        <v>-22.3157196994641</v>
+        <v>-32.42136946126411</v>
       </c>
       <c r="F60">
-        <v>-0.8298859474963448</v>
+        <v>-4.515649548901952</v>
       </c>
       <c r="G60">
-        <v>-13.26710639846835</v>
+        <v>-18.49755895324133</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.63862700591266</v>
       </c>
       <c r="E61">
-        <v>-22.31311582690969</v>
+        <v>-32.81081596168676</v>
       </c>
       <c r="F61">
-        <v>-1.258290232099957</v>
+        <v>-4.560177610272037</v>
       </c>
       <c r="G61">
-        <v>-13.64475531263108</v>
+        <v>-18.99737923033765</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.69750709224206</v>
       </c>
       <c r="E62">
-        <v>-21.55737691366562</v>
+        <v>-32.35707192306621</v>
       </c>
       <c r="F62">
-        <v>-0.9981240535353133</v>
+        <v>-4.374648163067032</v>
       </c>
       <c r="G62">
-        <v>-13.69175553024857</v>
+        <v>-19.77713200294565</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.73291982730366</v>
       </c>
       <c r="E63">
-        <v>-22.0526425304625</v>
+        <v>-31.69293498204929</v>
       </c>
       <c r="F63">
-        <v>-1.235949991613857</v>
+        <v>-4.318389590905903</v>
       </c>
       <c r="G63">
-        <v>-13.84005690107079</v>
+        <v>-20.01018568603755</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.74410873556775</v>
       </c>
       <c r="E64">
-        <v>-21.58657651406708</v>
+        <v>-31.40644560242803</v>
       </c>
       <c r="F64">
-        <v>-1.122945767258754</v>
+        <v>-4.38016923180669</v>
       </c>
       <c r="G64">
-        <v>-14.109558393245</v>
+        <v>-19.4873017025999</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.72305473356493</v>
       </c>
       <c r="E65">
-        <v>-21.18460651877622</v>
+        <v>-32.01186182098749</v>
       </c>
       <c r="F65">
-        <v>-1.273359063524283</v>
+        <v>-4.441504039412174</v>
       </c>
       <c r="G65">
-        <v>-13.49051493078626</v>
+        <v>-19.40653443391417</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.67010863603327</v>
       </c>
       <c r="E66">
-        <v>-20.69391013225307</v>
+        <v>-31.11391523848054</v>
       </c>
       <c r="F66">
-        <v>-1.279797963346243</v>
+        <v>-4.470448853200794</v>
       </c>
       <c r="G66">
-        <v>-13.78441066464417</v>
+        <v>-19.35327200495048</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.59636282572236</v>
       </c>
       <c r="E67">
-        <v>-20.65841595298095</v>
+        <v>-31.30989400811049</v>
       </c>
       <c r="F67">
-        <v>-1.322410010913653</v>
+        <v>-4.506337870927083</v>
       </c>
       <c r="G67">
-        <v>-13.42398488244696</v>
+        <v>-19.73281746517457</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.50437709287046</v>
       </c>
       <c r="E68">
-        <v>-21.29589829598872</v>
+        <v>-32.30179284085457</v>
       </c>
       <c r="F68">
-        <v>-1.474029410117657</v>
+        <v>-4.276494081141915</v>
       </c>
       <c r="G68">
-        <v>-14.14144038252735</v>
+        <v>-19.90241888574993</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.39550137895391</v>
       </c>
       <c r="E69">
-        <v>-20.027911988419</v>
+        <v>-31.39607766118747</v>
       </c>
       <c r="F69">
-        <v>-1.451787745352491</v>
+        <v>-4.548279769265627</v>
       </c>
       <c r="G69">
-        <v>-14.05202381381092</v>
+        <v>-19.54195372889401</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.26178826091186</v>
       </c>
       <c r="E70">
-        <v>-20.73942582450417</v>
+        <v>-31.13897807787599</v>
       </c>
       <c r="F70">
-        <v>-1.517510415090603</v>
+        <v>-4.5570008212823</v>
       </c>
       <c r="G70">
-        <v>-13.5810799270485</v>
+        <v>-19.41028487015662</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.10930066613216</v>
       </c>
       <c r="E71">
-        <v>-20.50076618735192</v>
+        <v>-31.25279900782179</v>
       </c>
       <c r="F71">
-        <v>-1.686068270947052</v>
+        <v>-4.705324974957969</v>
       </c>
       <c r="G71">
-        <v>-13.91727716925076</v>
+        <v>-19.4284579157636</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.94693285011768</v>
       </c>
       <c r="E72">
-        <v>-20.6122164611547</v>
+        <v>-31.22473152592224</v>
       </c>
       <c r="F72">
-        <v>-1.679758596439928</v>
+        <v>-4.980979138852755</v>
       </c>
       <c r="G72">
-        <v>-13.5932565402556</v>
+        <v>-19.30085941237069</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.77693289474936</v>
       </c>
       <c r="E73">
-        <v>-21.20647904823327</v>
+        <v>-31.64231569959155</v>
       </c>
       <c r="F73">
-        <v>-1.761201194380967</v>
+        <v>-4.682234233604932</v>
       </c>
       <c r="G73">
-        <v>-13.34840194382515</v>
+        <v>-19.16230326958002</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.59956964109373</v>
       </c>
       <c r="E74">
-        <v>-21.13853382422218</v>
+        <v>-31.81198629947394</v>
       </c>
       <c r="F74">
-        <v>-1.837057282557527</v>
+        <v>-4.828963780030212</v>
       </c>
       <c r="G74">
-        <v>-13.68158046219273</v>
+        <v>-19.6215758512555</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.4091679451098</v>
       </c>
       <c r="E75">
-        <v>-21.35967732391275</v>
+        <v>-30.85924291723718</v>
       </c>
       <c r="F75">
-        <v>-1.909563452957165</v>
+        <v>-4.788409397091356</v>
       </c>
       <c r="G75">
-        <v>-13.38335351587636</v>
+        <v>-18.68573044723237</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.21537550244763</v>
       </c>
       <c r="E76">
-        <v>-21.94550789238903</v>
+        <v>-31.69419842629743</v>
       </c>
       <c r="F76">
-        <v>-1.871099040975572</v>
+        <v>-5.214358400713071</v>
       </c>
       <c r="G76">
-        <v>-13.00885457441069</v>
+        <v>-18.61591917733363</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.02624318548932</v>
       </c>
       <c r="E77">
-        <v>-21.85923593406891</v>
+        <v>-32.42728591255513</v>
       </c>
       <c r="F77">
-        <v>-1.943125586648989</v>
+        <v>-4.824869988325577</v>
       </c>
       <c r="G77">
-        <v>-12.89898615171425</v>
+        <v>-18.9707406331073</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.84445633533951</v>
       </c>
       <c r="E78">
-        <v>-21.9221636088795</v>
+        <v>-31.38971289096969</v>
       </c>
       <c r="F78">
-        <v>-1.953546448576207</v>
+        <v>-5.198221803706536</v>
       </c>
       <c r="G78">
-        <v>-12.8417321167235</v>
+        <v>-18.3947041416282</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.66900877321469</v>
       </c>
       <c r="E79">
-        <v>-22.50367854162647</v>
+        <v>-33.52862211240559</v>
       </c>
       <c r="F79">
-        <v>-2.194927739547566</v>
+        <v>-5.077460746991618</v>
       </c>
       <c r="G79">
-        <v>-12.25101379937666</v>
+        <v>-18.11451078900254</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.49443862795493</v>
       </c>
       <c r="E80">
-        <v>-22.6362994314151</v>
+        <v>-32.58400054830158</v>
       </c>
       <c r="F80">
-        <v>-1.989413928750023</v>
+        <v>-5.155743123290978</v>
       </c>
       <c r="G80">
-        <v>-12.39149930044429</v>
+        <v>-18.97484051944582</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.32987302167514</v>
       </c>
       <c r="E81">
-        <v>-23.19801587580054</v>
+        <v>-33.1773506478676</v>
       </c>
       <c r="F81">
-        <v>-2.029957542912642</v>
+        <v>-5.254126662986669</v>
       </c>
       <c r="G81">
-        <v>-12.24183294145334</v>
+        <v>-17.99378644477667</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.17823227344066</v>
       </c>
       <c r="E82">
-        <v>-23.62824354889926</v>
+        <v>-33.57755453829547</v>
       </c>
       <c r="F82">
-        <v>-2.207856069603058</v>
+        <v>-5.313103936963786</v>
       </c>
       <c r="G82">
-        <v>-11.74755300696015</v>
+        <v>-17.63365105068748</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.03820314985688</v>
       </c>
       <c r="E83">
-        <v>-24.026006591837</v>
+        <v>-34.03968983925224</v>
       </c>
       <c r="F83">
-        <v>-2.186271300188311</v>
+        <v>-5.289082939017406</v>
       </c>
       <c r="G83">
-        <v>-11.5727721781532</v>
+        <v>-17.62491315767468</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.90326526596082</v>
       </c>
       <c r="E84">
-        <v>-24.975940055952</v>
+        <v>-34.96933347557587</v>
       </c>
       <c r="F84">
-        <v>-2.086875495526399</v>
+        <v>-5.123305084164752</v>
       </c>
       <c r="G84">
-        <v>-11.20587910826233</v>
+        <v>-16.89953678874979</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.76551614740407</v>
       </c>
       <c r="E85">
-        <v>-26.44639443640467</v>
+        <v>-35.97715442293093</v>
       </c>
       <c r="F85">
-        <v>-2.224993334432174</v>
+        <v>-5.478478376891276</v>
       </c>
       <c r="G85">
-        <v>-11.01030189721163</v>
+        <v>-16.52975788449739</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.63080866797062</v>
       </c>
       <c r="E86">
-        <v>-26.72551146034144</v>
+        <v>-35.68276059192928</v>
       </c>
       <c r="F86">
-        <v>-2.332362175346032</v>
+        <v>-5.328106498995887</v>
       </c>
       <c r="G86">
-        <v>-10.73340617225321</v>
+        <v>-16.65024598077098</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.49714829020471</v>
       </c>
       <c r="E87">
-        <v>-27.95445779349103</v>
+        <v>-36.84778751446061</v>
       </c>
       <c r="F87">
-        <v>-2.276008340933582</v>
+        <v>-5.402044088267563</v>
       </c>
       <c r="G87">
-        <v>-10.76219561021578</v>
+        <v>-17.49360195208726</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.36078653167479</v>
       </c>
       <c r="E88">
-        <v>-28.51783618783729</v>
+        <v>-37.85679718624268</v>
       </c>
       <c r="F88">
-        <v>-2.200826543822902</v>
+        <v>-5.405103249086102</v>
       </c>
       <c r="G88">
-        <v>-10.56297296201253</v>
+        <v>-16.3835253238684</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.21320265341234</v>
       </c>
       <c r="E89">
-        <v>-30.28765666375202</v>
+        <v>-38.98583632583505</v>
       </c>
       <c r="F89">
-        <v>-2.425261922835191</v>
+        <v>-5.400349248561435</v>
       </c>
       <c r="G89">
-        <v>-10.10623020215939</v>
+        <v>-16.73912442915166</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.04852211385637</v>
       </c>
       <c r="E90">
-        <v>-30.89537561134438</v>
+        <v>-40.65251627775108</v>
       </c>
       <c r="F90">
-        <v>-2.45866252488347</v>
+        <v>-5.683242515189286</v>
       </c>
       <c r="G90">
-        <v>-9.923492411070793</v>
+        <v>-16.73802193870769</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.872501877703877</v>
       </c>
       <c r="E91">
-        <v>-32.61440698702609</v>
+        <v>-40.95327940744452</v>
       </c>
       <c r="F91">
-        <v>-2.426006625130308</v>
+        <v>-5.948026842024537</v>
       </c>
       <c r="G91">
-        <v>-10.1843856184838</v>
+        <v>-16.52380738919934</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.682768457503286</v>
       </c>
       <c r="E92">
-        <v>-33.90074267127488</v>
+        <v>-41.51954243973366</v>
       </c>
       <c r="F92">
-        <v>-2.474058561431902</v>
+        <v>-5.760665046124539</v>
       </c>
       <c r="G92">
-        <v>-10.30762173781343</v>
+        <v>-16.36643836259759</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.477055684738186</v>
       </c>
       <c r="E93">
-        <v>-35.55674448148083</v>
+        <v>-42.82781178783861</v>
       </c>
       <c r="F93">
-        <v>-2.610688652482249</v>
+        <v>-5.912576859021732</v>
       </c>
       <c r="G93">
-        <v>-10.20116906676036</v>
+        <v>-16.52787446332227</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.248035805722392</v>
       </c>
       <c r="E94">
-        <v>-37.18299195321938</v>
+        <v>-44.32577891212488</v>
       </c>
       <c r="F94">
-        <v>-2.821718561815035</v>
+        <v>-6.003710527208122</v>
       </c>
       <c r="G94">
-        <v>-10.4087982045989</v>
+        <v>-16.83895887631932</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.998417461945632</v>
       </c>
       <c r="E95">
-        <v>-38.66071227021735</v>
+        <v>-46.20034072760002</v>
       </c>
       <c r="F95">
-        <v>-2.840102519585364</v>
+        <v>-6.033447260233819</v>
       </c>
       <c r="G95">
-        <v>-10.70186050818071</v>
+        <v>-16.95086657821496</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.734671722610017</v>
       </c>
       <c r="E96">
-        <v>-40.13300973959114</v>
+        <v>-47.33792056917086</v>
       </c>
       <c r="F96">
-        <v>-2.83507681455258</v>
+        <v>-6.19424745536305</v>
       </c>
       <c r="G96">
-        <v>-10.68565783612017</v>
+        <v>-17.25611369805777</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.460634190544297</v>
       </c>
       <c r="E97">
-        <v>-42.15087737927602</v>
+        <v>-48.40141457597622</v>
       </c>
       <c r="F97">
-        <v>-2.684896289527237</v>
+        <v>-6.112044416146242</v>
       </c>
       <c r="G97">
-        <v>-11.02980547816097</v>
+        <v>-17.12896144079695</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.175957297323812</v>
       </c>
       <c r="E98">
-        <v>-43.68391300627768</v>
+        <v>-49.67526299314887</v>
       </c>
       <c r="F98">
-        <v>-2.860527574636191</v>
+        <v>-6.118190073907611</v>
       </c>
       <c r="G98">
-        <v>-11.00932737440848</v>
+        <v>-17.01808240186019</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.883232826946811</v>
       </c>
       <c r="E99">
-        <v>-46.02747528930522</v>
+        <v>-51.04471768568996</v>
       </c>
       <c r="F99">
-        <v>-2.952249383678569</v>
+        <v>-6.385134782929363</v>
       </c>
       <c r="G99">
-        <v>-11.18382273693975</v>
+        <v>-17.57786700295536</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.585091091454867</v>
       </c>
       <c r="E100">
-        <v>-47.83206765288785</v>
+        <v>-51.49934590886051</v>
       </c>
       <c r="F100">
-        <v>-3.08038788048282</v>
+        <v>-6.555189498682671</v>
       </c>
       <c r="G100">
-        <v>-11.28246610068133</v>
+        <v>-18.39482390621512</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.300624465347648</v>
       </c>
       <c r="E101">
-        <v>-49.53745134002894</v>
+        <v>-52.67061080433741</v>
       </c>
       <c r="F101">
-        <v>-3.242269095072704</v>
+        <v>-6.498194093716752</v>
       </c>
       <c r="G101">
-        <v>-11.48884509310573</v>
+        <v>-18.17441605101332</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.018653318753445</v>
       </c>
       <c r="E102">
-        <v>-51.51336380015125</v>
+        <v>-54.7449281367649</v>
       </c>
       <c r="F102">
-        <v>-3.263480270788789</v>
+        <v>-6.504562582309474</v>
       </c>
       <c r="G102">
-        <v>-12.0156353708099</v>
+        <v>-18.6613427679918</v>
       </c>
     </row>
   </sheetData>
